--- a/artfynd/S 1155-2026 artfynd.xlsx
+++ b/artfynd/S 1155-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY100"/>
+  <dimension ref="A1:AZ100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441419</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441393</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441392</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441421</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441413</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441435</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441441</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1501,6 +1541,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441442</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,6 +1647,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441443</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1703,6 +1753,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441455</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1804,6 +1859,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441425</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1918,6 +1978,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441422</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2032,6 +2097,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441423</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2146,6 +2216,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441394</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2260,6 +2335,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441395</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2374,6 +2454,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441396</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2488,6 +2573,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441397</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2602,6 +2692,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441401</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2716,6 +2811,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441402</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2830,6 +2930,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441403</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2944,6 +3049,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441404</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3058,6 +3168,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441405</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3172,6 +3287,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441406</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3286,6 +3406,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441408</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3400,6 +3525,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441417</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3514,6 +3644,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441418</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3615,6 +3750,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441436</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3716,6 +3856,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441437</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3817,6 +3962,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441438</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3918,6 +4068,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441439</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4019,6 +4174,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441440</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4120,6 +4280,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441444</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4221,6 +4386,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441445</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4322,6 +4492,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441447</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4423,6 +4598,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441448</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4524,6 +4704,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441449</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4625,6 +4810,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441450</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4726,6 +4916,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127441432</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4827,6 +5022,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122744997</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4926,6 +5126,11 @@
       <c r="AY41" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122748032</t>
         </is>
       </c>
     </row>
@@ -5029,6 +5234,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119748233</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5130,6 +5340,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122744998</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5229,6 +5444,11 @@
       <c r="AY44" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122744999</t>
         </is>
       </c>
     </row>
@@ -5332,6 +5552,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119748096</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5433,6 +5658,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119748101</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5534,6 +5764,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747820</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5635,6 +5870,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122745017</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5734,6 +5974,11 @@
       <c r="AY49" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122748042</t>
         </is>
       </c>
     </row>
@@ -5837,6 +6082,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119748124</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5938,6 +6188,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119748137</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6039,6 +6294,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747852</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6140,6 +6400,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747884</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6241,6 +6506,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119748127</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6342,6 +6612,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119748163</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6443,6 +6718,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119748035</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6544,6 +6824,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747812</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6649,6 +6934,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747819</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6750,6 +7040,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747856</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6851,6 +7146,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747878</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6952,6 +7252,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747885</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7053,6 +7358,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747942</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7154,6 +7464,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747972</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7255,6 +7570,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747987</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7356,6 +7676,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119748154</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7457,6 +7782,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119748185</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7562,6 +7892,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119748211</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7663,6 +7998,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747948</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7762,6 +8102,11 @@
       <c r="AY69" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122745009</t>
         </is>
       </c>
     </row>
@@ -7865,6 +8210,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119748180</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7975,6 +8325,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747902</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8076,6 +8431,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747982</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8177,6 +8537,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119748025</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8278,6 +8643,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122745004</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8377,6 +8747,11 @@
       <c r="AY75" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122745018</t>
         </is>
       </c>
     </row>
@@ -8480,6 +8855,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747923</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8581,6 +8961,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747985</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8686,6 +9071,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119748003</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8787,6 +9177,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119748072</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8892,6 +9287,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119748193</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8997,6 +9397,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122745010</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9099,6 +9504,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747838</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9201,6 +9611,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747892</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9303,6 +9718,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747910</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9405,6 +9825,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747929</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9507,6 +9932,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119747989</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9613,6 +10043,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122745005</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9714,6 +10149,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118072217</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9820,6 +10260,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118072262</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9922,6 +10367,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118072473</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10023,6 +10473,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118072273</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10124,6 +10579,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118072288</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10225,6 +10685,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118072535</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10326,6 +10791,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118072557</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10434,6 +10904,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118072529</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10536,6 +11011,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118072545</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10638,6 +11118,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118072500</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10745,6 +11230,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119833961</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10852,6 +11342,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119834160</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10959,8 +11454,114 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119833980</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>